--- a/docs/03.  Iteration Features Log TEMPLATE.xlsx
+++ b/docs/03.  Iteration Features Log TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marve\Desktop\RenCloud\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55EA79B-FDBF-4548-8231-553C17F71D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E769347-C28F-44AC-895A-A588D4B14152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="30">
   <si>
     <t>Iteration #1</t>
   </si>
@@ -120,6 +120,12 @@
   </si>
   <si>
     <t>BUILDING USER INTERFACE</t>
+  </si>
+  <si>
+    <t>Oct 28 2024</t>
+  </si>
+  <si>
+    <t>Loading_Form created, fully functional and has a logic that does the behaviour you want after completion which will be used on further stages of the application. After successfully optimising the code so it can be shared among the forms, now the smooth animations and round corners with fancy borders are just a 10 seconds question.</t>
   </si>
 </sst>
 </file>
@@ -514,7 +520,7 @@
     <col min="1" max="1" width="26.90625" customWidth="1"/>
     <col min="2" max="2" width="71.7265625" customWidth="1"/>
     <col min="3" max="3" width="33.81640625" customWidth="1"/>
-    <col min="4" max="4" width="26.26953125" customWidth="1"/>
+    <col min="4" max="4" width="59.6328125" customWidth="1"/>
     <col min="5" max="7" width="27.54296875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -552,7 +558,7 @@
         <v>26</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>13</v>
@@ -633,7 +639,9 @@
       <c r="C6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>

--- a/docs/03.  Iteration Features Log TEMPLATE.xlsx
+++ b/docs/03.  Iteration Features Log TEMPLATE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marve\Desktop\RenCloud\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E769347-C28F-44AC-895A-A588D4B14152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092D6513-3587-430F-B557-F866CF94B595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="32">
   <si>
     <t>Iteration #1</t>
   </si>
@@ -95,21 +95,9 @@
     <t>Not Implemented.</t>
   </si>
   <si>
-    <t xml:space="preserve">Implemented: LogIn_Form, </t>
-  </si>
-  <si>
-    <t>UserInterface_Form.</t>
-  </si>
-  <si>
     <t>PasswordRestore_Form.</t>
   </si>
   <si>
-    <t>Register_Form.</t>
-  </si>
-  <si>
-    <t>Loading_Form, UserInterface_Form, Register_Form, PasswordRestore_Form.</t>
-  </si>
-  <si>
     <t>First main form to be opened, also includes the methods to be used for next Forms, which will drastically speed up creation of new forms.</t>
   </si>
   <si>
@@ -126,6 +114,24 @@
   </si>
   <si>
     <t>Loading_Form created, fully functional and has a logic that does the behaviour you want after completion which will be used on further stages of the application. After successfully optimising the code so it can be shared among the forms, now the smooth animations and round corners with fancy borders are just a 10 seconds question.</t>
+  </si>
+  <si>
+    <t>Nov 04 2024</t>
+  </si>
+  <si>
+    <t>Registration_Form.</t>
+  </si>
+  <si>
+    <t>Registration_Form created, fully functional and has validation logic for the box inputs, there are 3 more textbox inputs that must have validation which will be created at a later stage of the app development, in short words the UI design is almost there, fully functional with no need for improvements which is a very big step. After the PasswordRestore_Form, I will start working on UserInterface_Form because of all the validation and logic behind the app, the complex parts of the application will be just a matter of time.</t>
+  </si>
+  <si>
+    <t>UserInterface_Form</t>
+  </si>
+  <si>
+    <t>Implemented: LogIn_Form, Loading_Form, Registration_Form</t>
+  </si>
+  <si>
+    <t>UserInterface_Form, PasswordRestore_Form.</t>
   </si>
 </sst>
 </file>
@@ -192,13 +198,13 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -521,7 +527,8 @@
     <col min="2" max="2" width="71.7265625" customWidth="1"/>
     <col min="3" max="3" width="33.81640625" customWidth="1"/>
     <col min="4" max="4" width="59.6328125" customWidth="1"/>
-    <col min="5" max="7" width="27.54296875" customWidth="1"/>
+    <col min="5" max="5" width="88.08984375" customWidth="1"/>
+    <col min="6" max="7" width="27.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -529,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -555,13 +562,13 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>13</v>
@@ -584,13 +591,13 @@
         <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
@@ -598,16 +605,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>18</v>
@@ -621,7 +628,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -630,19 +637,21 @@
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>

--- a/docs/03.  Iteration Features Log TEMPLATE.xlsx
+++ b/docs/03.  Iteration Features Log TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marve\Desktop\RenCloud\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092D6513-3587-430F-B557-F866CF94B595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F19BD17-53CB-4905-B539-0E33758C3EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
   <si>
     <t>Iteration #1</t>
   </si>
@@ -128,10 +128,19 @@
     <t>UserInterface_Form</t>
   </si>
   <si>
-    <t>Implemented: LogIn_Form, Loading_Form, Registration_Form</t>
-  </si>
-  <si>
     <t>UserInterface_Form, PasswordRestore_Form.</t>
+  </si>
+  <si>
+    <t>Nov 07 2024</t>
+  </si>
+  <si>
+    <t>FormManager</t>
+  </si>
+  <si>
+    <t>Implemented: LogIn_Form, Loading_Form, Registration_Form, FormManager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After lot of work I started to pay attention to the performance, after serveral tests I realised that the app does not dispose of anything whatsoever which results in unnecessary memory usage, after carefuly analising the problem and the documentation I decided to create a Form Manager that would allow me to easily change between the forms without the need to create new instances and dispose them all the time, also I did write new disposal functions that dispose of any resource as soon as it is not in use which resulted in an increase from 350mb usage or StackOverflows to 100-160 mb constant memory usage. During it lots of cool features were added from the design and navigation perspective for users, ton of bugs fixed, and validation for every single entrie in the app. </t>
   </si>
 </sst>
 </file>
@@ -520,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.90625" customWidth="1"/>
@@ -528,10 +537,12 @@
     <col min="3" max="3" width="33.81640625" customWidth="1"/>
     <col min="4" max="4" width="59.6328125" customWidth="1"/>
     <col min="5" max="5" width="88.08984375" customWidth="1"/>
-    <col min="6" max="7" width="27.54296875" customWidth="1"/>
+    <col min="6" max="6" width="129.90625" customWidth="1"/>
+    <col min="7" max="7" width="27.54296875" customWidth="1"/>
+    <col min="8" max="8" width="22.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -553,8 +564,11 @@
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -571,13 +585,16 @@
         <v>26</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="H2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -594,18 +611,21 @@
         <v>27</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -617,26 +637,30 @@
         <v>17</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="H4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -652,10 +676,13 @@
       <c r="E6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="2"/>
+      <c r="F6" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="G6" s="2"/>
-    </row>
-    <row r="9" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="H6" s="2"/>
+    </row>
+    <row r="9" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -666,7 +693,7 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -677,7 +704,7 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -688,7 +715,7 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
@@ -699,7 +726,7 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -710,7 +737,7 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>

--- a/docs/03.  Iteration Features Log TEMPLATE.xlsx
+++ b/docs/03.  Iteration Features Log TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marve\Desktop\RenCloud\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F19BD17-53CB-4905-B539-0E33758C3EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D57F1B9-FE81-473D-AFAF-83407798144C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="35">
   <si>
     <t>Iteration #1</t>
   </si>
@@ -92,9 +92,6 @@
     <t>Implemented.</t>
   </si>
   <si>
-    <t>Not Implemented.</t>
-  </si>
-  <si>
     <t>PasswordRestore_Form.</t>
   </si>
   <si>
@@ -125,12 +122,6 @@
     <t>Registration_Form created, fully functional and has validation logic for the box inputs, there are 3 more textbox inputs that must have validation which will be created at a later stage of the app development, in short words the UI design is almost there, fully functional with no need for improvements which is a very big step. After the PasswordRestore_Form, I will start working on UserInterface_Form because of all the validation and logic behind the app, the complex parts of the application will be just a matter of time.</t>
   </si>
   <si>
-    <t>UserInterface_Form</t>
-  </si>
-  <si>
-    <t>UserInterface_Form, PasswordRestore_Form.</t>
-  </si>
-  <si>
     <t>Nov 07 2024</t>
   </si>
   <si>
@@ -141,6 +132,15 @@
   </si>
   <si>
     <t xml:space="preserve">After lot of work I started to pay attention to the performance, after serveral tests I realised that the app does not dispose of anything whatsoever which results in unnecessary memory usage, after carefuly analising the problem and the documentation I decided to create a Form Manager that would allow me to easily change between the forms without the need to create new instances and dispose them all the time, also I did write new disposal functions that dispose of any resource as soon as it is not in use which resulted in an increase from 350mb usage or StackOverflows to 100-160 mb constant memory usage. During it lots of cool features were added from the design and navigation perspective for users, ton of bugs fixed, and validation for every single entrie in the app. </t>
+  </si>
+  <si>
+    <t>Nov 08 2024</t>
+  </si>
+  <si>
+    <t>All bugs fixed and all validation is now done, the UserInterface_Form would be in deficit for this iteration because next what I will work on is code optimisation, there is a lot of optimisations to be done in order to follow the code standards, everything else such as application performance and resource usage is optimised, for next iteration I will finish the UserInterface_Form first because this is the mos crucial and important part of the application, because of my code features implemented the development of new features will be very easy there will be no need to make validations and look for security threats withing the app, this application should be done by iteration 3 or iteration 4, which will give me time to even better optimise the app and the process of rendering, in short words trying to apply the most recent technologies and best practices if needed.</t>
+  </si>
+  <si>
+    <t>UserInterface_Form.</t>
   </si>
 </sst>
 </file>
@@ -529,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.90625" customWidth="1"/>
@@ -538,16 +538,15 @@
     <col min="4" max="4" width="59.6328125" customWidth="1"/>
     <col min="5" max="5" width="88.08984375" customWidth="1"/>
     <col min="6" max="6" width="129.90625" customWidth="1"/>
-    <col min="7" max="7" width="27.54296875" customWidth="1"/>
-    <col min="8" max="8" width="22.08984375" customWidth="1"/>
+    <col min="7" max="7" width="136.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -564,11 +563,8 @@
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -576,25 +572,22 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -608,24 +601,21 @@
         <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -640,49 +630,46 @@
         <v>17</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="9" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -693,7 +680,7 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -704,7 +691,7 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -715,7 +702,7 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
@@ -726,7 +713,7 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -737,7 +724,7 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
